--- a/assets/data/excel/quest.xlsx
+++ b/assets/data/excel/quest.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>累计消耗赛博币</t>
+          <t>累计消耗菌丝</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">

--- a/assets/data/excel/quest.xlsx
+++ b/assets/data/excel/quest.xlsx
@@ -1,7 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定每日任务" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="随机任务池" sheetId="2" state="visible" r:id="rId2"/>
@@ -9,55 +13,31 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完成奖励" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-        <bgColor rgb="0070AD47"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -65,32 +45,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -237,7 +202,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -272,7 +236,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -307,16 +270,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -438,46 +405,7 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -488,188 +416,175 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>questId</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>targetParam</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>targetValue</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rewardReputation</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>rewardCoins</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>isFixed</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>任务ID</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>分类</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>目标参数</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>目标值</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>声望奖励</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>金币奖励</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>菌丝奖励</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>是否固定</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>权重</t>
         </is>
@@ -678,17 +593,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>探索禁区</t>
+          <t>每日登录</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>进入禁区并完成1层探索</t>
+          <t>登录游戏</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -698,22 +613,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>explore</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>complete_floor</t>
+          <t>login</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -725,17 +640,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>每日登录</t>
+          <t>探索禁区</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>登录游戏</t>
+          <t>进入禁区并完成1层探索</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -745,22 +660,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>explore</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>login</t>
+          <t>complete_floor</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -819,17 +734,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>探索禁区</t>
+          <t>招募融合姬</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>进入禁区并完成1层探索</t>
+          <t>在庇护所招募新融合姬</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -839,22 +754,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>explore</t>
+          <t>manage</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>complete_floor</t>
+          <t>recruit</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -866,17 +781,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>招募伙伴</t>
+          <t>禁区探索</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>在基地招募新角色</t>
+          <t>完成一次禁区探索</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -886,12 +801,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>manage</t>
+          <t>explore</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>recruit</t>
+          <t>complete_explore</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -901,7 +816,7 @@
         <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -913,17 +828,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>战斗胜利</t>
+          <t>升级设施</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>赢得战斗胜利</t>
+          <t>升级任意基地设施</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -933,263 +848,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>battle</t>
+          <t>manage</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>battle_win</t>
+          <t>upgrade_facility</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I9" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>D05</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>使用能量饮料</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>购买并使用能量饮料</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>manage</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>use_energy_drink</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>10</v>
-      </c>
-      <c r="I10" t="n">
-        <v>100</v>
-      </c>
-      <c r="J10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>招募伙伴</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>在基地招募新角色</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>manage</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>recruit</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>10</v>
-      </c>
-      <c r="I11" t="n">
-        <v>150</v>
-      </c>
-      <c r="J11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>D06</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>升级设施</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>升级任意基地设施</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>manage</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>upgrade_facility</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>15</v>
-      </c>
-      <c r="I12" t="n">
-        <v>250</v>
-      </c>
-      <c r="J12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>D05</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>使用能量饮料</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>购买并使用能量饮料</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>manage</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>use_energy_drink</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="n">
-        <v>100</v>
-      </c>
-      <c r="J13" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>D06</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>升级设施</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>升级任意基地设施</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>manage</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>upgrade_facility</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>15</v>
-      </c>
-      <c r="I15" t="n">
-        <v>250</v>
-      </c>
-      <c r="J15" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1204,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1267,111 +946,131 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>string</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>宝箱猎人</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>开启宝箱</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>explore</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>open_chest</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>25</v>
-      </c>
-      <c r="I2" t="n">
-        <v>400</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>10</v>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>任务ID</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>登高者-10</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>到达第10层</t>
+          <t>描述</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>类型</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>explore</t>
+          <t>分类</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>reach_floor</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" t="n">
-        <v>30</v>
-      </c>
-      <c r="I3" t="n">
-        <v>500</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>8</v>
+          <t>目标参数</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>目标值</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>声望奖励</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>菌丝奖励</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>是否固定</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R03</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>登高者-20</t>
+          <t>宝箱猎人</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>到达第20层</t>
+          <t>开启宝箱</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1386,39 +1085,39 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>reach_floor</t>
+          <t>open_chest</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I4" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R04</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>登高者-30</t>
+          <t>登高者-10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>到达第30层</t>
+          <t>到达第10层</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1437,35 +1136,35 @@
         </is>
       </c>
       <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="n">
         <v>30</v>
       </c>
-      <c r="H5" t="n">
-        <v>50</v>
-      </c>
       <c r="I5" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R05</t>
+          <t>R03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>连续探索</t>
+          <t>登高者-20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>连续探索不退出</t>
+          <t>到达第20层</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1480,39 +1179,39 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>consecutive_floors</t>
+          <t>reach_floor</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" t="n">
+        <v>40</v>
+      </c>
+      <c r="I6" t="n">
+        <v>600</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>35</v>
-      </c>
-      <c r="I6" t="n">
-        <v>550</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R06</t>
+          <t>R04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>自动探索</t>
+          <t>登高者-30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>使用自动探索功能</t>
+          <t>到达第30层</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1527,39 +1226,39 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>auto_explore</t>
+          <t>reach_floor</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I7" t="n">
+        <v>700</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>20</v>
-      </c>
-      <c r="I7" t="n">
-        <v>350</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R07</t>
+          <t>R05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BOSS挑战者</t>
+          <t>连续探索</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>挑战BOSS（无论胜负）</t>
+          <t>连续探索不退出</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1574,39 +1273,39 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>challenge_boss</t>
+          <t>consecutive_floors</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I8" t="n">
-        <v>800</v>
+        <v>550</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R08</t>
+          <t>R06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>暴击专家</t>
+          <t>自动探索</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>造成暴击</t>
+          <t>使用自动探索功能</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1616,22 +1315,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>battle</t>
+          <t>explore</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>critical_hit</t>
+          <t>auto_explore</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I9" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1643,17 +1342,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R09</t>
+          <t>R07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>无伤通关</t>
+          <t>BOSS挑战者</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>单层无角色死亡通关</t>
+          <t>挑战BOSS（无论胜负）</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1663,44 +1362,44 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>battle</t>
+          <t>explore</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>no_death_clear</t>
+          <t>challenge_boss</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I10" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>技能释放者</t>
+          <t>暴击专家</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>使用技能攻击</t>
+          <t>造成暴击</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1715,17 +1414,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>use_skill</t>
+          <t>critical_hit</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I11" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1737,17 +1436,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>快速战斗</t>
+          <t>无伤通关</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>30秒内结束战斗</t>
+          <t>单层无融合姬阵亡通关</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1762,39 +1461,39 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>speed_battle</t>
+          <t>no_death_clear</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I12" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>以少胜多</t>
+          <t>技能释放者</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>用≤3人队伍击败敌人</t>
+          <t>使用技能攻击</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1809,39 +1508,39 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>outnumbered_win</t>
+          <t>use_skill</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I13" t="n">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>强化装备</t>
+          <t>快速战斗</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>强化装备成功</t>
+          <t>30秒内结束战斗</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1851,44 +1550,44 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>manage</t>
+          <t>battle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>enhance_equip</t>
+          <t>speed_battle</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I14" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>刷新伙伴</t>
+          <t>以少胜多</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>睡一觉刷新伙伴</t>
+          <t>用≤3人队伍击败敌人</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1898,44 +1597,44 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>manage</t>
+          <t>battle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>refresh_partner</t>
+          <t>outnumbered_win</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="I15" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>大手笔消费</t>
+          <t>强化装备</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>累计消耗菌丝</t>
+          <t>强化装备成功</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1950,39 +1649,39 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>spend_coins</t>
+          <t>enhance_equip</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>5000</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I16" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>设施满级</t>
+          <t>完成抽卡</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>将任意设施升到下一级</t>
+          <t>完成一次抽卡</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1997,39 +1696,39 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>facility_upgrade</t>
+          <t>gacha_once</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I17" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R17</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>收集狂人</t>
+          <t>大手笔消费</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>招募3个不同职业的角色</t>
+          <t>累计消耗菌丝</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2044,22 +1743,116 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>recruit_different_class</t>
+          <t>spend_coins</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>5000</v>
       </c>
       <c r="H18" t="n">
         <v>25</v>
       </c>
       <c r="I18" t="n">
+        <v>450</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>设施满级</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>将任意设施升到下一级</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>manage</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>facility_upgrade</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>20</v>
+      </c>
+      <c r="I19" t="n">
+        <v>350</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>收集狂人</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>招募3个不同职业的融合姬</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>manage</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>recruit_different_class</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>25</v>
+      </c>
+      <c r="I20" t="n">
         <v>400</v>
       </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2074,7 +1867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2132,132 +1925,236 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W01</t>
+          <t>string</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周常探索者</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>本周累计探索楼层</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>explore</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>weekly_floors</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H2" t="n">
-        <v>80</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W02</t>
+          <t>任务ID</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周常战士</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>本周累计战斗胜利</t>
+          <t>描述</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>类型</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>battle</t>
+          <t>分类</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>weekly_battle_win</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>30</v>
-      </c>
-      <c r="H3" t="n">
-        <v>80</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
+          <t>目标参数</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>目标值</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>声望奖励</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>菌丝奖励</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>重置日</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>W01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>周常探索者</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>本周累计探索楼层</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>explore</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>weekly_floors</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" t="n">
+        <v>80</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>周常战士</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>本周累计战斗胜利</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>battle</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>weekly_battle_win</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" t="n">
+        <v>80</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>W03</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>周常经营者</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>本周累计招募角色</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>本周累计招募融合姬</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>manage</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>weekly_recruit</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G6" t="n">
         <v>10</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H6" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I6" t="n">
         <v>1200</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J6" t="n">
         <v>1</v>
       </c>
     </row>

--- a/assets/data/excel/quest.xlsx
+++ b/assets/data/excel/quest.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>rewardCoins</t>
+          <t>rewardMycelium</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
